--- a/Hardware/PickAndPlace_PCB1_2026_07_16.xlsx
+++ b/Hardware/PickAndPlace_PCB1_2026_07_16.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_16" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_08_04" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="166">
   <si>
     <t>Designator</t>
   </si>
@@ -58,6 +58,387 @@
     <t>Name</t>
   </si>
   <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>STM32F103C8T6-Card</t>
+  </si>
+  <si>
+    <t>CONN-TH_L53.3-W22.9_STM32F103C8T6-CARD</t>
+  </si>
+  <si>
+    <t>47.986mm</t>
+  </si>
+  <si>
+    <t>-33.871mm</t>
+  </si>
+  <si>
+    <t>55.606mm</t>
+  </si>
+  <si>
+    <t>-58.001mm</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>ESP8266-01S</t>
+  </si>
+  <si>
+    <t>WIFIM-TH_ESP8266-01S</t>
+  </si>
+  <si>
+    <t>16.109mm</t>
+  </si>
+  <si>
+    <t>-71.336mm</t>
+  </si>
+  <si>
+    <t>14.839mm</t>
+  </si>
+  <si>
+    <t>-75.146mm</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>DHT11</t>
+  </si>
+  <si>
+    <t>29.083mm</t>
+  </si>
+  <si>
+    <t>-13.589mm</t>
+  </si>
+  <si>
+    <t>-11.049mm</t>
+  </si>
+  <si>
+    <t>MQ7</t>
+  </si>
+  <si>
+    <t>MQ2</t>
+  </si>
+  <si>
+    <t>-6.858mm</t>
+  </si>
+  <si>
+    <t>-40.005mm</t>
+  </si>
+  <si>
+    <t>-36.195mm</t>
+  </si>
+  <si>
+    <t>-6.878mm</t>
+  </si>
+  <si>
+    <t>-21.171mm</t>
+  </si>
+  <si>
+    <t>-17.361mm</t>
+  </si>
+  <si>
+    <t>OLED1</t>
+  </si>
+  <si>
+    <t>MC096GW</t>
+  </si>
+  <si>
+    <t>OLED-TH_4P-L27.8-W27.3_MC096GW</t>
+  </si>
+  <si>
+    <t>7.6mm</t>
+  </si>
+  <si>
+    <t>-84.163mm</t>
+  </si>
+  <si>
+    <t>3.79mm</t>
+  </si>
+  <si>
+    <t>SPK1</t>
+  </si>
+  <si>
+    <t>ZX-XH2.54-2PZZ</t>
+  </si>
+  <si>
+    <t>CONN-TH_2P-P2.50_HX25003-2A</t>
+  </si>
+  <si>
+    <t>82.911mm</t>
+  </si>
+  <si>
+    <t>-88.1mm</t>
+  </si>
+  <si>
+    <t>84.161mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>JQ8900语音模块</t>
+  </si>
+  <si>
+    <t>JQ8900语音模块_1</t>
+  </si>
+  <si>
+    <t>77.831mm</t>
+  </si>
+  <si>
+    <t>-72.161mm</t>
+  </si>
+  <si>
+    <t>86.721mm</t>
+  </si>
+  <si>
+    <t>-72.225mm</t>
+  </si>
+  <si>
+    <t>68.941mm</t>
+  </si>
+  <si>
+    <t>-79.972mm</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>RGB单灯珠模块</t>
+  </si>
+  <si>
+    <t>35.286mm</t>
+  </si>
+  <si>
+    <t>-72.479mm</t>
+  </si>
+  <si>
+    <t>35.413mm</t>
+  </si>
+  <si>
+    <t>-71.209mm</t>
+  </si>
+  <si>
+    <t>39.096mm</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>LD2410C</t>
+  </si>
+  <si>
+    <t>-15.202mm</t>
+  </si>
+  <si>
+    <t>-10.122mm</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>SR501</t>
+  </si>
+  <si>
+    <t>HC-SR501_W32_H24</t>
+  </si>
+  <si>
+    <t>73.259mm</t>
+  </si>
+  <si>
+    <t>4.483mm</t>
+  </si>
+  <si>
+    <t>75.799mm</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>C0603</t>
+  </si>
+  <si>
+    <t>7.369mm</t>
+  </si>
+  <si>
+    <t>2.144mm</t>
+  </si>
+  <si>
+    <t>1.444mm</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>CL10A106KP8NNNC</t>
+  </si>
+  <si>
+    <t>7.346mm</t>
+  </si>
+  <si>
+    <t>5.626mm</t>
+  </si>
+  <si>
+    <t>6.326mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>CGA0603X5R226M160JT</t>
+  </si>
+  <si>
+    <t>19.032mm</t>
+  </si>
+  <si>
+    <t>5.576mm</t>
+  </si>
+  <si>
+    <t>6.276mm</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>19.03mm</t>
+  </si>
+  <si>
+    <t>1.689mm</t>
+  </si>
+  <si>
+    <t>0.989mm</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>有源蜂鸣器模块</t>
+  </si>
+  <si>
+    <t>55.098mm</t>
+  </si>
+  <si>
+    <t>-75.4mm</t>
+  </si>
+  <si>
+    <t>57.638mm</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>ZW101</t>
+  </si>
+  <si>
+    <t>30.988mm</t>
+  </si>
+  <si>
+    <t>5.207mm</t>
+  </si>
+  <si>
+    <t>43.18mm</t>
+  </si>
+  <si>
+    <t>0.254mm</t>
+  </si>
+  <si>
+    <t>24.638mm</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>AMS1117-3.3</t>
+  </si>
+  <si>
+    <t>SOT-89-3_L4.5-W2.5-P1.50-LS4.2-BR</t>
+  </si>
+  <si>
+    <t>13.23mm</t>
+  </si>
+  <si>
+    <t>4.339mm</t>
+  </si>
+  <si>
+    <t>14.73mm</t>
+  </si>
+  <si>
+    <t>5.695mm</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>火焰传感器模块</t>
+  </si>
+  <si>
+    <t>22.358mm</t>
+  </si>
+  <si>
+    <t>-54.333mm</t>
+  </si>
+  <si>
+    <t>24.618mm</t>
+  </si>
+  <si>
+    <t>-47.333mm</t>
+  </si>
+  <si>
+    <t>-50.523mm</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>0603WAF5101T5E</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>1.631mm</t>
+  </si>
+  <si>
+    <t>-4.28mm</t>
+  </si>
+  <si>
+    <t>2.384mm</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>-5.735mm</t>
+  </si>
+  <si>
+    <t>-6.488mm</t>
+  </si>
+  <si>
     <t>USB2</t>
   </si>
   <si>
@@ -79,240 +460,45 @@
     <t>0.579mm</t>
   </si>
   <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>火焰传感器模块</t>
-  </si>
-  <si>
-    <t>22.358mm</t>
-  </si>
-  <si>
-    <t>-54.333mm</t>
-  </si>
-  <si>
-    <t>24.618mm</t>
-  </si>
-  <si>
-    <t>-47.333mm</t>
-  </si>
-  <si>
-    <t>-50.523mm</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>AMS1117-3.3</t>
-  </si>
-  <si>
-    <t>SOT-89-3_L4.5-W2.5-P1.50-LS4.2-BR</t>
-  </si>
-  <si>
-    <t>13.865mm</t>
-  </si>
-  <si>
-    <t>4.085mm</t>
-  </si>
-  <si>
-    <t>15.365mm</t>
-  </si>
-  <si>
-    <t>5.441mm</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>SR501</t>
-  </si>
-  <si>
-    <t>HC-SR501_W32_H24</t>
-  </si>
-  <si>
-    <t>73.259mm</t>
-  </si>
-  <si>
-    <t>4.483mm</t>
-  </si>
-  <si>
-    <t>75.799mm</t>
-  </si>
-  <si>
-    <t>U10</t>
-  </si>
-  <si>
-    <t>ZW101</t>
-  </si>
-  <si>
-    <t>41.128mm</t>
-  </si>
-  <si>
-    <t>2.832mm</t>
-  </si>
-  <si>
-    <t>53.32mm</t>
-  </si>
-  <si>
-    <t>-2.121mm</t>
-  </si>
-  <si>
-    <t>34.778mm</t>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
-    <t>LD2410C</t>
-  </si>
-  <si>
-    <t>86.721mm</t>
-  </si>
-  <si>
-    <t>-15.202mm</t>
-  </si>
-  <si>
-    <t>-10.122mm</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>RGB单灯珠模块</t>
-  </si>
-  <si>
-    <t>35.286mm</t>
-  </si>
-  <si>
-    <t>-72.479mm</t>
-  </si>
-  <si>
-    <t>35.413mm</t>
-  </si>
-  <si>
-    <t>-71.209mm</t>
-  </si>
-  <si>
-    <t>39.096mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>JQ8900语音模块</t>
-  </si>
-  <si>
-    <t>JQ8900语音模块_1</t>
-  </si>
-  <si>
-    <t>77.831mm</t>
-  </si>
-  <si>
-    <t>-72.161mm</t>
-  </si>
-  <si>
-    <t>-72.225mm</t>
-  </si>
-  <si>
-    <t>68.941mm</t>
-  </si>
-  <si>
-    <t>-79.972mm</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>有源蜂鸣器模块</t>
-  </si>
-  <si>
-    <t>55.098mm</t>
-  </si>
-  <si>
-    <t>-75.4mm</t>
-  </si>
-  <si>
-    <t>57.638mm</t>
-  </si>
-  <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>ESP8266-01S</t>
-  </si>
-  <si>
-    <t>WIFIM-TH_ESP8266-01S</t>
-  </si>
-  <si>
-    <t>16.109mm</t>
-  </si>
-  <si>
-    <t>-71.336mm</t>
-  </si>
-  <si>
-    <t>14.839mm</t>
-  </si>
-  <si>
-    <t>-75.146mm</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>STM32F103C8T6-Card</t>
-  </si>
-  <si>
-    <t>CONN-TH_L53.3-W22.9_STM32F103C8T6-CARD</t>
-  </si>
-  <si>
-    <t>47.986mm</t>
-  </si>
-  <si>
-    <t>-33.871mm</t>
-  </si>
-  <si>
-    <t>55.606mm</t>
-  </si>
-  <si>
-    <t>-58.001mm</t>
-  </si>
-  <si>
-    <t>SPK1</t>
-  </si>
-  <si>
-    <t>ZX-XH2.54-2PZZ</t>
-  </si>
-  <si>
-    <t>CONN-TH_2P-P2.50_HX25003-2A</t>
-  </si>
-  <si>
-    <t>82.911mm</t>
-  </si>
-  <si>
-    <t>-88.1mm</t>
-  </si>
-  <si>
-    <t>84.161mm</t>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>TS665CJ</t>
+  </si>
+  <si>
+    <t>SW-TH_4P-L6.0-W6.0-P4.50-LS6.5</t>
+  </si>
+  <si>
+    <t>81.006mm</t>
+  </si>
+  <si>
+    <t>-54.826mm</t>
+  </si>
+  <si>
+    <t>77.756mm</t>
+  </si>
+  <si>
+    <t>-52.576mm</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>80.879mm</t>
+  </si>
+  <si>
+    <t>-44.539mm</t>
+  </si>
+  <si>
+    <t>77.629mm</t>
+  </si>
+  <si>
+    <t>-42.289mm</t>
   </si>
   <si>
     <t>S3</t>
   </si>
   <si>
-    <t>TS665CJ</t>
-  </si>
-  <si>
-    <t>SW-TH_4P-L6.0-W6.0-P4.50-LS6.5</t>
-  </si>
-  <si>
     <t>80.625mm</t>
   </si>
   <si>
@@ -323,189 +509,6 @@
   </si>
   <si>
     <t>-32.764mm</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>80.879mm</t>
-  </si>
-  <si>
-    <t>-44.539mm</t>
-  </si>
-  <si>
-    <t>77.629mm</t>
-  </si>
-  <si>
-    <t>-42.289mm</t>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>81.006mm</t>
-  </si>
-  <si>
-    <t>-54.826mm</t>
-  </si>
-  <si>
-    <t>77.756mm</t>
-  </si>
-  <si>
-    <t>-52.576mm</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>0603WAF5101T5E</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>-5.735mm</t>
-  </si>
-  <si>
-    <t>-4.28mm</t>
-  </si>
-  <si>
-    <t>-6.488mm</t>
-  </si>
-  <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>1.631mm</t>
-  </si>
-  <si>
-    <t>2.384mm</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>DHT11</t>
-  </si>
-  <si>
-    <t>17.76mm</t>
-  </si>
-  <si>
-    <t>-12.789mm</t>
-  </si>
-  <si>
-    <t>-10.249mm</t>
-  </si>
-  <si>
-    <t>OLED1</t>
-  </si>
-  <si>
-    <t>MC096GW</t>
-  </si>
-  <si>
-    <t>OLED-TH_4P-L27.8-W27.3_MC096GW</t>
-  </si>
-  <si>
-    <t>7.6mm</t>
-  </si>
-  <si>
-    <t>-84.163mm</t>
-  </si>
-  <si>
-    <t>3.79mm</t>
-  </si>
-  <si>
-    <t>MQ7</t>
-  </si>
-  <si>
-    <t>MQ2</t>
-  </si>
-  <si>
-    <t>12.553mm</t>
-  </si>
-  <si>
-    <t>-40.094mm</t>
-  </si>
-  <si>
-    <t>-36.284mm</t>
-  </si>
-  <si>
-    <t>-26.759mm</t>
-  </si>
-  <si>
-    <t>-22.949mm</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB104</t>
-  </si>
-  <si>
-    <t>C0603</t>
-  </si>
-  <si>
-    <t>19.665mm</t>
-  </si>
-  <si>
-    <t>1.435mm</t>
-  </si>
-  <si>
-    <t>0.735mm</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>CGA0603X5R226M160JT</t>
-  </si>
-  <si>
-    <t>19.667mm</t>
-  </si>
-  <si>
-    <t>5.322mm</t>
-  </si>
-  <si>
-    <t>6.022mm</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>CL10A106KP8NNNC</t>
-  </si>
-  <si>
-    <t>7.981mm</t>
-  </si>
-  <si>
-    <t>5.372mm</t>
-  </si>
-  <si>
-    <t>6.072mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>8.004mm</t>
-  </si>
-  <si>
-    <t>1.89mm</t>
-  </si>
-  <si>
-    <t>1.19mm</t>
   </si>
 </sst>
 </file>
@@ -964,13 +967,13 @@
         <v>21</v>
       </c>
       <c r="J2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
         <v>22</v>
       </c>
       <c r="L2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M2" t="s">
         <v>23</v>
@@ -990,34 +993,34 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
       </c>
       <c r="I3" t="s">
         <v>30</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K3" t="s">
         <v>22</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
@@ -1037,25 +1040,25 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" t="s">
         <v>33</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
         <v>35</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -1064,10 +1067,10 @@
         <v>22</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N4" t="s">
         <v>32</v>
@@ -1078,175 +1081,175 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
         <v>39</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" t="s">
         <v>40</v>
       </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>43</v>
-      </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="s">
         <v>22</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M5" t="s">
         <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K6" t="s">
         <v>22</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="O6" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K7" t="s">
         <v>22</v>
       </c>
       <c r="L7">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="O7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K8" t="s">
         <v>22</v>
@@ -1258,39 +1261,39 @@
         <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" t="s">
         <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" t="s">
-        <v>71</v>
       </c>
       <c r="J9">
         <v>16</v>
@@ -1305,42 +1308,42 @@
         <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="O9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G10" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="H10" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="s">
         <v>22</v>
@@ -1352,133 +1355,133 @@
         <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="O10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K11" t="s">
         <v>22</v>
       </c>
       <c r="L11">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M11" t="s">
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I12" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J12">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="K12" t="s">
         <v>22</v>
       </c>
       <c r="L12">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
         <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="O12" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1487,280 +1490,280 @@
         <v>22</v>
       </c>
       <c r="L13">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M13" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O13" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F14" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="H14" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K14" t="s">
         <v>22</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B15" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" t="s">
+        <v>84</v>
+      </c>
+      <c r="D15" t="s">
         <v>98</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>99</v>
       </c>
-      <c r="D15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E15" t="s">
-        <v>106</v>
-      </c>
       <c r="F15" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G15" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="s">
         <v>22</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M15" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="F16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G16" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="H16" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K16" t="s">
         <v>22</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="O16" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F17" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G17" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="H17" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="I17" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" t="s">
         <v>22</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M17" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N17" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="O17" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" t="s">
         <v>115</v>
       </c>
-      <c r="C18" t="s">
+      <c r="G18" t="s">
         <v>116</v>
       </c>
-      <c r="D18" t="s">
-        <v>122</v>
-      </c>
-      <c r="E18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" t="s">
-        <v>118</v>
-      </c>
       <c r="H18" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="I18" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J18">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K18" t="s">
         <v>22</v>
       </c>
       <c r="L18">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N18" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="O18" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" t="s">
         <v>124</v>
-      </c>
-      <c r="B19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" t="s">
-        <v>125</v>
-      </c>
-      <c r="D19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" t="s">
-        <v>127</v>
-      </c>
-      <c r="F19" t="s">
-        <v>126</v>
-      </c>
-      <c r="G19" t="s">
-        <v>128</v>
-      </c>
-      <c r="H19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" t="s">
-        <v>128</v>
       </c>
       <c r="J19">
         <v>3</v>
@@ -1769,45 +1772,45 @@
         <v>22</v>
       </c>
       <c r="L19">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M19" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N19" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O19" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" t="s">
+        <v>126</v>
+      </c>
+      <c r="D20" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F20" t="s">
         <v>129</v>
       </c>
-      <c r="B20" t="s">
+      <c r="G20" t="s">
         <v>130</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" t="s">
         <v>131</v>
-      </c>
-      <c r="D20" t="s">
-        <v>132</v>
-      </c>
-      <c r="E20" t="s">
-        <v>133</v>
-      </c>
-      <c r="F20" t="s">
-        <v>132</v>
-      </c>
-      <c r="G20" t="s">
-        <v>133</v>
-      </c>
-      <c r="H20" t="s">
-        <v>134</v>
-      </c>
-      <c r="I20" t="s">
-        <v>133</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -1822,104 +1825,104 @@
         <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="O20" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" t="s">
+        <v>134</v>
+      </c>
+      <c r="D21" t="s">
         <v>135</v>
       </c>
-      <c r="B21" t="s">
+      <c r="E21" t="s">
         <v>136</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F21" t="s">
+        <v>135</v>
+      </c>
+      <c r="G21" t="s">
         <v>136</v>
-      </c>
-      <c r="D21" t="s">
-        <v>137</v>
-      </c>
-      <c r="E21" t="s">
-        <v>138</v>
-      </c>
-      <c r="F21" t="s">
-        <v>137</v>
-      </c>
-      <c r="G21" t="s">
-        <v>139</v>
       </c>
       <c r="H21" t="s">
         <v>137</v>
       </c>
       <c r="I21" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" t="s">
         <v>22</v>
       </c>
       <c r="L21">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O21" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>139</v>
+      </c>
+      <c r="B22" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" t="s">
         <v>136</v>
       </c>
-      <c r="B22" t="s">
+      <c r="F22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" t="s">
         <v>136</v>
       </c>
-      <c r="C22" t="s">
+      <c r="H22" t="s">
+        <v>141</v>
+      </c>
+      <c r="I22" t="s">
         <v>136</v>
       </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F22" t="s">
-        <v>137</v>
-      </c>
-      <c r="G22" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" t="s">
-        <v>137</v>
-      </c>
-      <c r="I22" t="s">
-        <v>141</v>
-      </c>
       <c r="J22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K22" t="s">
         <v>22</v>
       </c>
       <c r="L22">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M22" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="O22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -1945,28 +1948,28 @@
         <v>146</v>
       </c>
       <c r="H23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J23">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K23" t="s">
         <v>22</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M23" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="O23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1977,54 +1980,54 @@
         <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E24" t="s">
+        <v>153</v>
+      </c>
+      <c r="F24" t="s">
         <v>152</v>
       </c>
-      <c r="F24" t="s">
-        <v>151</v>
-      </c>
       <c r="G24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H24" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K24" t="s">
         <v>22</v>
       </c>
       <c r="L24">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N24" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="O24" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D25" t="s">
         <v>157</v>
@@ -2039,28 +2042,28 @@
         <v>158</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K25" t="s">
         <v>22</v>
       </c>
       <c r="L25">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M25" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N25" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="O25" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -2068,10 +2071,10 @@
         <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C26" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s">
         <v>162</v>
@@ -2086,28 +2089,28 @@
         <v>163</v>
       </c>
       <c r="H26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K26" t="s">
         <v>22</v>
       </c>
       <c r="L26">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="N26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O26" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
